--- a/public/PAPAssessmentTemplate.xlsx
+++ b/public/PAPAssessmentTemplate.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hr\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\assessment_dashboard\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7F9C2C-92EC-4422-A86F-E8768824BCD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12390" windowHeight="4725"/>
+    <workbookView xWindow="4065" yWindow="4065" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="modulequestions" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>question</t>
   </si>
@@ -45,12 +46,15 @@
   </si>
   <si>
     <t>maxMarks</t>
+  </si>
+  <si>
+    <t>STOP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -80,8 +84,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -363,7 +367,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G55"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -399,6 +403,11 @@
         <v>6</v>
       </c>
     </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+    </row>
     <row r="22" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C22" s="1"/>
     </row>
